--- a/buhbase/Бухгалтеры_Барнаул_пилот.xlsx
+++ b/buhbase/Бухгалтеры_Барнаул_пилот.xlsx
@@ -8,9 +8,10 @@
   </bookViews>
   <sheets>
     <sheet name="База A-B-C" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Сводка" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'База A-B-C'!$A$1:$I$53</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'База A-B-C'!$A$1:$K$53</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -19,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -31,8 +32,11 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
+    <font>
+      <color rgb="00808080"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -47,6 +51,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
     <fill>
@@ -67,17 +76,34 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -443,18 +469,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I53"/>
+  <dimension ref="A1:K53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="46" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
-    <col width="46" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="46" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
     <col width="46" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="46" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -465,40 +493,50 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Качество</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Осн. контакт</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Организация / ФИО</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Город</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Профиль</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Источник (2ГИС)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Сайт</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Пометка</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Дата сбора</t>
         </is>
@@ -510,38 +548,48 @@
           <t>C</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>ядро</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
         <is>
           <t>buh.profi13@mail.ru</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Бухгалтер Профи</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Барнаул</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Барнаул</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
         <is>
           <t>Бухгалтерские услуги</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>https://2gis.ru/barnaul/firm/70000001037817334</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>buhgalterprofi.2gis.biz</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
         <is>
           <t>2026-09-18</t>
         </is>
@@ -553,38 +601,48 @@
           <t>C</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>ядро</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
         <is>
           <t>hi@hnh.li</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Head&amp;Heart, бухгалтерская компания</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Барнаул</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Барнаул</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
         <is>
           <t>Бухгалтерские услуги</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>https://2gis.ru/barnaul/firm/70000001029445436</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>hnh.li</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
         <is>
           <t>2026-09-18</t>
         </is>
@@ -596,38 +654,48 @@
           <t>C</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>ядро</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
         <is>
           <t>info@ecp-tandem.ru</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Тандем, центр поддержки и развития бизнеса</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Барнаул</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Барнаул</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
         <is>
           <t>Бухгалтерские услуги</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>https://2gis.ru/barnaul/firm/563478235331716</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>ecp-tandem.ru</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
         <is>
           <t>2026-09-18</t>
         </is>
@@ -639,38 +707,48 @@
           <t>C</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>ядро</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
         <is>
           <t>info@1-plus-1.ru</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>1+1, бухгалтерские и юридические услуги</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Барнаул</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Барнаул</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
         <is>
           <t>Бухгалтерские услуги</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>https://2gis.ru/barnaul/firm/563479234920287</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>1-plus-1.ru</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
         <is>
           <t>2026-09-18</t>
         </is>
@@ -682,85 +760,105 @@
           <t>C</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>ядро</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
         <is>
           <t>info@altbd.ru</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Бухгалтерский дом, бухгалтерская компания</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Барнаул</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Барнаул</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
         <is>
           <t>Бухгалтерские услуги</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>https://2gis.ru/barnaul/firm/563478234959090</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>altbd.ru</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr">
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
         <is>
           <t>2026-09-18</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>ядро</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
         <is>
           <t>sales@altbd.ru</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="E7" s="6" t="inlineStr">
         <is>
           <t>Бухгалтерский дом, бухгалтерская компания</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Барнаул</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>Барнаул</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
         <is>
           <t>Бухгалтерские услуги</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="H7" s="6" t="inlineStr">
         <is>
           <t>https://2gis.ru/barnaul/firm/563478234959090</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="I7" s="6" t="inlineStr">
         <is>
           <t>altbd.ru</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="J7" s="6" t="inlineStr">
         <is>
           <t>второй адрес той же компании</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="K7" s="6" t="inlineStr">
         <is>
           <t>2026-09-18</t>
         </is>
@@ -772,38 +870,48 @@
           <t>C</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>ядро</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
         <is>
           <t>1c@aitis.pro</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>АЙТИС, официальный партнёр 1С</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Барнаул</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Барнаул</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
         <is>
           <t>Бухгалтерские услуги / 1С</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>https://2gis.ru/barnaul/firm/70000001035464179</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>aitis.pro</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr">
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
         <is>
           <t>2026-09-18</t>
         </is>
@@ -815,38 +923,48 @@
           <t>C</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>ядро</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
         <is>
           <t>dcfinance@mail.ru</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>Dress Code Finance</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Барнаул</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Барнаул</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
         <is>
           <t>Бухгалтерские услуги</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>https://2gis.ru/barnaul/firm/70000001116316599</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>dcfin.ru</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr">
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
         <is>
           <t>2026-09-18</t>
         </is>
@@ -858,34 +976,43 @@
           <t>C</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>ядро</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
         <is>
           <t>256953@bk.ru</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>Бухгалтерия без проблем</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Барнаул</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Барнаул</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
         <is>
           <t>Бухгалтерские услуги</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>https://2gis.ru/barnaul/firm/70000001026564648</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr">
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
         <is>
           <t>2026-09-18</t>
         </is>
@@ -897,34 +1024,43 @@
           <t>C</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>ядро</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
         <is>
           <t>ajur.2005@yandex.ru</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>Ажур, бухгалтерский центр</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Барнаул</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Барнаул</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
         <is>
           <t>Бухгалтерские услуги</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>https://2gis.ru/barnaul/firm/563478234742023</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr">
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
         <is>
           <t>2026-09-18</t>
         </is>
@@ -936,38 +1072,48 @@
           <t>C</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>ядро</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
         <is>
           <t>kan700@yandex.ru</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>Канцлер, бухгалтерские и юридические услуги</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Барнаул</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Барнаул</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
         <is>
           <t>Бухгалтерские услуги</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>https://2gis.ru/barnaul/firm/563478234992658</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>kancler.pro</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr">
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
         <is>
           <t>2026-09-18</t>
         </is>
@@ -979,38 +1125,48 @@
           <t>C</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>ядро</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
         <is>
           <t>info@cbt-22.ru</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>Центр Бухгалтерских Технологий</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Барнаул</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Барнаул</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
         <is>
           <t>Бухгалтерские услуги</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>https://2gis.ru/barnaul/firm/70000001113230088</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>cbt-22.ru</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr">
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
         <is>
           <t>2026-09-18</t>
         </is>
@@ -1022,34 +1178,43 @@
           <t>C</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>ядро</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
         <is>
           <t>audit-profi97@mail.ru</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>Аудит-Профи, аудиторская организация</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Барнаул</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Барнаул</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
         <is>
           <t>Аудит / бухучёт</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>https://2gis.ru/barnaul/firm/563478234419811</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr">
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
         <is>
           <t>2026-09-18</t>
         </is>
@@ -1061,85 +1226,105 @@
           <t>C</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>ядро</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
         <is>
           <t>kontur@kea22.ru</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>Контур-Экстерн Алтай</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Барнаул</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Барнаул</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
         <is>
           <t>Бухгалтерские услуги / ЭДО</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>https://2gis.ru/barnaul/firm/563478234596675</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>kea22.ru</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr">
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
         <is>
           <t>2026-09-18</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>ядро</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
         <is>
           <t>sic@kea22.ru</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="E16" s="6" t="inlineStr">
         <is>
           <t>Контур-Экстерн Алтай</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Барнаул</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>Барнаул</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
         <is>
           <t>Бухгалтерские услуги / ЭДО</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="H16" s="6" t="inlineStr">
         <is>
           <t>https://2gis.ru/barnaul/firm/563478234596675</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="I16" s="6" t="inlineStr">
         <is>
           <t>kea22.ru</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="J16" s="6" t="inlineStr">
         <is>
           <t>второй адрес той же компании</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="K16" s="6" t="inlineStr">
         <is>
           <t>2026-09-18</t>
         </is>
@@ -1151,42 +1336,52 @@
           <t>C</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>ядро</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
         <is>
           <t>buh-law@list.ru</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>Бизнес решения, бухгалтерско-юридическая компания</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Барнаул</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Барнаул</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
         <is>
           <t>Бухгалтерские услуги</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>https://2gis.ru/barnaul/firm/70000001045575497</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>business-resheniya.ru</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>маркер buh- в адресе</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>2026-09-18</t>
         </is>
@@ -1198,42 +1393,52 @@
           <t>C</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>спорная</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
         <is>
           <t>svetlana897@mail.ru</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>Бизнес решения, бухгалтерско-юридическая компания</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Барнаул</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Барнаул</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
         <is>
           <t>Бухгалтерские услуги</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>https://2gis.ru/barnaul/firm/70000001045575497</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>business-resheniya.ru</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>(?) личный адрес на сайте компании, роль не подписана</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>2026-09-18</t>
         </is>
@@ -1245,38 +1450,48 @@
           <t>C</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>ядро</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
         <is>
           <t>oper@prox-it.ru</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>Компания ПРОКС, отдел заполнения деклараций</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Барнаул</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Барнаул</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
         <is>
           <t>Бухгалтерские услуги</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>https://2gis.ru/barnaul/firm/563478234404306</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>prox-it.ru</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr">
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
         <is>
           <t>2026-09-18</t>
         </is>
@@ -1288,38 +1503,48 @@
           <t>C</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>ядро</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
         <is>
           <t>r13014@ya.ru</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>АБС Консалтинг</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Барнаул</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Барнаул</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
         <is>
           <t>Бухгалтерские услуги</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>https://2gis.ru/barnaul/firm/70000001113058074</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>абсконсалтинг.рф</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr">
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
         <is>
           <t>2026-09-18</t>
         </is>
@@ -1331,38 +1556,48 @@
           <t>C</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>ядро</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
         <is>
           <t>info@bis-alt.ru</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>БизнесИнфоСервис</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Барнаул</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Барнаул</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
         <is>
           <t>Бухгалтерские услуги / ПО</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>https://2gis.ru/barnaul/firm/563479234675481</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>bis-alt.ru</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr">
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
         <is>
           <t>2026-09-18</t>
         </is>
@@ -1374,85 +1609,105 @@
           <t>C</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>ядро</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
         <is>
           <t>1c@1c-galex.ru</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>1С-Галэкс, официальный партнёр 1С</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Барнаул</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Барнаул</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
         <is>
           <t>Бухгалтерские услуги / 1С</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>https://2gis.ru/barnaul/firm/563478234399077</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>1c-galex.ru</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr">
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
         <is>
           <t>2026-09-18</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>ядро</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
         <is>
           <t>partner@1c-galex.ru</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="E23" s="6" t="inlineStr">
         <is>
           <t>1С-Галэкс, официальный партнёр 1С</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Барнаул</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>Барнаул</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
         <is>
           <t>Бухгалтерские услуги / 1С</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="H23" s="6" t="inlineStr">
         <is>
           <t>https://2gis.ru/barnaul/firm/563478234399077</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="I23" s="6" t="inlineStr">
         <is>
           <t>1c-galex.ru</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="J23" s="6" t="inlineStr">
         <is>
           <t>второй адрес той же компании</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="K23" s="6" t="inlineStr">
         <is>
           <t>2026-09-18</t>
         </is>
@@ -1464,38 +1719,48 @@
           <t>C</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>ядро</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
         <is>
           <t>apps-lex@mail.ru</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>АППС</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Барнаул</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Барнаул</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
         <is>
           <t>Бухгалтерские услуги</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>https://2gis.ru/barnaul/firm/70000001034472537</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>apps-lex.ru</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr">
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
         <is>
           <t>2026-09-18</t>
         </is>
@@ -1507,38 +1772,48 @@
           <t>C</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>ядро</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
         <is>
           <t>rs.light@mail.ru</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>Лайт, бухгалтерский центр</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Барнаул</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Барнаул</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
         <is>
           <t>Бухгалтерские услуги</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>https://2gis.ru/barnaul/firm/563478235337768</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>light22.ru</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr">
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
         <is>
           <t>2026-09-18</t>
         </is>
@@ -1550,38 +1825,48 @@
           <t>C</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>ядро</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
         <is>
           <t>reglament22@mail.ru</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>Регламент, центр практической бухгалтерии</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Барнаул</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Барнаул</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
         <is>
           <t>Бухгалтерские услуги</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>https://2gis.ru/barnaul/firm/563478235194530</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>reglament22.ru</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr">
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
         <is>
           <t>2026-09-18</t>
         </is>
@@ -1593,42 +1878,52 @@
           <t>C</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>спорная</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
         <is>
           <t>eltrace@internet.ru</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>СБИС ЭПД, IT-компания</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Барнаул</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Барнаул</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
         <is>
           <t>Бухгалтерские услуги / ЭДО</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>https://2gis.ru/barnaul/firm/70000001110796005</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>etrn.shop</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>(?) профиль ближе к ЭДО, чем к бухучёту</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="K27" t="inlineStr">
         <is>
           <t>2026-09-18</t>
         </is>
@@ -1640,38 +1935,48 @@
           <t>C</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>ядро</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
         <is>
           <t>info@nalog-off.net</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>Налог-офф.Нет, бухгалтерская компания</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Барнаул</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Барнаул</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
         <is>
           <t>Бухгалтерские услуги</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>https://2gis.ru/barnaul/firm/70000001040587747</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>nalog-off.net</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr">
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
         <is>
           <t>2026-09-18</t>
         </is>
@@ -1683,42 +1988,52 @@
           <t>C</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>спорная</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
         <is>
           <t>info@znanie22.ru</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>Знание, учебный центр</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Барнаул</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Барнаул</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
         <is>
           <t>Бухгалтерские курсы / аудит</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>https://2gis.ru/barnaul/firm/563478235311602</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>znanie22.ru</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t>(?) учебный центр, бухуслуги как доп. направление</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="K29" t="inlineStr">
         <is>
           <t>2026-09-18</t>
         </is>
@@ -1730,85 +2045,105 @@
           <t>C</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>ядро</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
         <is>
           <t>support@1cbo.ru</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>Касс-мастер / 1С:БухОбслуживание</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Барнаул</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Барнаул</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
         <is>
           <t>1С:БухОбслуживание</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>https://2gis.ru/barnaul/firm/563478234619573</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>kvc1c.ru</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr">
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
         <is>
           <t>2026-09-18</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>ядро</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
         <is>
           <t>1cbo.help@mail.ru</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="E31" s="6" t="inlineStr">
         <is>
           <t>Касс-мастер / 1С:БухОбслуживание</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Барнаул</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
+      <c r="F31" s="6" t="inlineStr">
+        <is>
+          <t>Барнаул</t>
+        </is>
+      </c>
+      <c r="G31" s="6" t="inlineStr">
         <is>
           <t>1С:БухОбслуживание</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="H31" s="6" t="inlineStr">
         <is>
           <t>https://2gis.ru/barnaul/firm/563478234619573</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="I31" s="6" t="inlineStr">
         <is>
           <t>kvc1c.ru</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="J31" s="6" t="inlineStr">
         <is>
           <t>второй адрес той же компании</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="K31" s="6" t="inlineStr">
         <is>
           <t>2026-09-18</t>
         </is>
@@ -1820,38 +2155,48 @@
           <t>C</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>ядро</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
         <is>
           <t>info@t-valtron.ru</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>ТехноВальтрон</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Барнаул</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Барнаул</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
         <is>
           <t>Бухгалтерские услуги</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>https://2gis.ru/barnaul/firm/70000001075268045</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>t-valtron.ru</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr">
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
         <is>
           <t>2026-09-18</t>
         </is>
@@ -1863,42 +2208,52 @@
           <t>C</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>ядро</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
         <is>
           <t>dir@t-valtron.ru</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>ТехноВальтрон</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Барнаул</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Барнаул</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
         <is>
           <t>Бухгалтерские услуги</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t>https://2gis.ru/barnaul/firm/70000001075268045</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t>t-valtron.ru</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t>адрес руководителя</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="K33" t="inlineStr">
         <is>
           <t>2026-09-18</t>
         </is>
@@ -1910,38 +2265,48 @@
           <t>C</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>ядро</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
         <is>
           <t>office@finansburg.ru</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>Финансбург</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Барнаул</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Барнаул</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
         <is>
           <t>Бухгалтерские услуги</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t>https://2gis.ru/barnaul/firm/70000001033975992</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>finansburg.ru</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr">
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
         <is>
           <t>2026-09-18</t>
         </is>
@@ -1953,38 +2318,48 @@
           <t>C</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>ядро</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
         <is>
           <t>r_tf@mail.ru</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>Радек</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Барнаул</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Барнаул</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
         <is>
           <t>Аудит / бухучёт</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="H35" t="inlineStr">
         <is>
           <t>https://2gis.ru/barnaul/firm/70000001007487426</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t>radek-audit.ru</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr">
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
         <is>
           <t>2026-09-18</t>
         </is>
@@ -1996,38 +2371,48 @@
           <t>C</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>ядро</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
         <is>
           <t>info@afibs.ru</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>Афибс, агентство фин. и бух. сопровождения</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Барнаул</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Барнаул</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
         <is>
           <t>Аудит / бухучёт</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="H36" t="inlineStr">
         <is>
           <t>https://2gis.ru/barnaul/firm/563479234924242</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="I36" t="inlineStr">
         <is>
           <t>afibs.ru</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr">
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
         <is>
           <t>2026-09-18</t>
         </is>
@@ -2039,38 +2424,48 @@
           <t>C</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>ядро</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
         <is>
           <t>barnaulkonsalting@mail.ru</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>Консалтинг-аудит, аудиторская фирма</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Барнаул</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Барнаул</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
         <is>
           <t>Аудиторские услуги</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t>https://2gis.ru/barnaul/firm/563478234403674</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t>cons-audit.ru</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr">
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
         <is>
           <t>2026-09-18</t>
         </is>
@@ -2082,38 +2477,48 @@
           <t>C</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>ядро</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
         <is>
           <t>auditbarnaul@yandex.ru</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>Инаудит Барнаул</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Барнаул</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Барнаул</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
         <is>
           <t>Аудит / бухучёт</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="H38" t="inlineStr">
         <is>
           <t>https://2gis.ru/barnaul/firm/70000001094155511</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="I38" t="inlineStr">
         <is>
           <t>inauditbarnaul.ru</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr">
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
         <is>
           <t>2026-09-18</t>
         </is>
@@ -2125,85 +2530,105 @@
           <t>C</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>ядро</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
         <is>
           <t>auditb@mail.ru</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>Русский альянс, аудиторская компания</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Барнаул</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Барнаул</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
         <is>
           <t>Аудит / бухучёт</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t>https://2gis.ru/barnaul/firm/70000001092852735</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t>auditb.ru</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr">
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
         <is>
           <t>2026-09-18</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>ядро</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
         <is>
           <t>audit@dsmail.ru</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="E40" s="6" t="inlineStr">
         <is>
           <t>Русский альянс, аудиторская компания</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Барнаул</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
+      <c r="F40" s="6" t="inlineStr">
+        <is>
+          <t>Барнаул</t>
+        </is>
+      </c>
+      <c r="G40" s="6" t="inlineStr">
         <is>
           <t>Аудит / бухучёт</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="H40" s="6" t="inlineStr">
         <is>
           <t>https://2gis.ru/barnaul/firm/70000001092852735</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="I40" s="6" t="inlineStr">
         <is>
           <t>auditb.ru</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="J40" s="6" t="inlineStr">
         <is>
           <t>второй адрес той же компании</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
+      <c r="K40" s="6" t="inlineStr">
         <is>
           <t>2026-09-18</t>
         </is>
@@ -2215,38 +2640,48 @@
           <t>C</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>ядро</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
         <is>
           <t>info@prodengi22.ru</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>Про деньги, центр для бизнеса</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Барнаул</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Барнаул</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
         <is>
           <t>Аудит / бухучёт</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="H41" t="inlineStr">
         <is>
           <t>https://2gis.ru/barnaul/firm/70000001089574098</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t>prodengi22.ru</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr">
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
         <is>
           <t>2026-09-18</t>
         </is>
@@ -2258,85 +2693,105 @@
           <t>C</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>ядро</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
         <is>
           <t>finauditbarnaul@mail.ru</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>Финаудит, бухгалтерско-аудиторская фирма</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>Барнаул</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Барнаул</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
         <is>
           <t>Аудит / бухучёт</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="H42" t="inlineStr">
         <is>
           <t>https://2gis.ru/barnaul/firm/563478234401045</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t>finauditbarnaul.ru</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr">
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
         <is>
           <t>2026-09-18</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>ядро</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
         <is>
           <t>finaudit@alt.ru</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="E43" s="6" t="inlineStr">
         <is>
           <t>Финаудит, бухгалтерско-аудиторская фирма</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>Барнаул</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
+      <c r="F43" s="6" t="inlineStr">
+        <is>
+          <t>Барнаул</t>
+        </is>
+      </c>
+      <c r="G43" s="6" t="inlineStr">
         <is>
           <t>Аудит / бухучёт</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="H43" s="6" t="inlineStr">
         <is>
           <t>https://2gis.ru/barnaul/firm/563478234401045</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="I43" s="6" t="inlineStr">
         <is>
           <t>finauditbarnaul.ru</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="J43" s="6" t="inlineStr">
         <is>
           <t>второй адрес той же компании</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
+      <c r="K43" s="6" t="inlineStr">
         <is>
           <t>2026-09-18</t>
         </is>
@@ -2348,38 +2803,48 @@
           <t>C</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>ядро</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
         <is>
           <t>bs.commerc@mail.ru</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>Бс Коммерц</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>Барнаул</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Барнаул</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
         <is>
           <t>Аудит / бухучёт</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="H44" t="inlineStr">
         <is>
           <t>https://2gis.ru/barnaul/firm/70000001089239087</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="I44" t="inlineStr">
         <is>
           <t>bs-commerc.ru</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr">
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
         <is>
           <t>2026-09-18</t>
         </is>
@@ -2391,38 +2856,48 @@
           <t>C</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>ядро</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
         <is>
           <t>profbalans22@mail.ru</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="E45" t="inlineStr">
         <is>
           <t>Профбаланс</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>Барнаул</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Барнаул</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
         <is>
           <t>Бухгалтерские услуги</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="H45" t="inlineStr">
         <is>
           <t>https://2gis.ru/barnaul/firm/70000001064620393</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="I45" t="inlineStr">
         <is>
           <t>profbalans22.ru</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr">
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
         <is>
           <t>2026-09-18</t>
         </is>
@@ -2434,38 +2909,48 @@
           <t>C</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>ядро</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
         <is>
           <t>info@bkons.ru</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>Бизнес консультант</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>Барнаул</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Барнаул</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
         <is>
           <t>Бухгалтерские услуги</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="H46" t="inlineStr">
         <is>
           <t>https://2gis.ru/barnaul/firm/563479234592915</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="I46" t="inlineStr">
         <is>
           <t>bkons.ru</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr">
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
         <is>
           <t>2026-09-18</t>
         </is>
@@ -2477,42 +2962,52 @@
           <t>C</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B47" s="7" t="inlineStr">
+        <is>
+          <t>спорная</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
         <is>
           <t>zakaz@etalon-altai.ru</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="E47" t="inlineStr">
         <is>
           <t>Эталон, Алтайский центр печатей</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>Барнаул</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Барнаул</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
         <is>
           <t>Бухгалтерские услуги / печати</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="H47" t="inlineStr">
         <is>
           <t>https://2gis.ru/barnaul/firm/70000001037299823</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="I47" t="inlineStr">
         <is>
           <t>etalon-altai.ru</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="J47" t="inlineStr">
         <is>
           <t>(?) бухуслуги как доп. направление</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
+      <c r="K47" t="inlineStr">
         <is>
           <t>2026-09-18</t>
         </is>
@@ -2524,89 +3019,109 @@
           <t>C</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B48" s="7" t="inlineStr">
+        <is>
+          <t>спорная</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
         <is>
           <t>office@garant-altay.ru</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t>Гарант, информационный центр</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>Барнаул</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Барнаул</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
         <is>
           <t>Правовые системы / бухуслуги</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="H48" t="inlineStr">
         <is>
           <t>https://2gis.ru/barnaul/firm/563478234401358</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="I48" t="inlineStr">
         <is>
           <t>garant-barnaul.ru</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="J48" t="inlineStr">
         <is>
           <t>(?) профиль ближе к правовым системам</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
+      <c r="K48" t="inlineStr">
         <is>
           <t>2026-09-18</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B49" s="8" t="inlineStr">
+        <is>
+          <t>спорная</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="D49" s="6" t="inlineStr">
         <is>
           <t>sales@garant-altay.ru</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="E49" s="6" t="inlineStr">
         <is>
           <t>Гарант, информационный центр</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>Барнаул</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
+      <c r="F49" s="6" t="inlineStr">
+        <is>
+          <t>Барнаул</t>
+        </is>
+      </c>
+      <c r="G49" s="6" t="inlineStr">
         <is>
           <t>Правовые системы / бухуслуги</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="H49" s="6" t="inlineStr">
         <is>
           <t>https://2gis.ru/barnaul/firm/563478234401358</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="I49" s="6" t="inlineStr">
         <is>
           <t>garant-barnaul.ru</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
+      <c r="J49" s="6" t="inlineStr">
         <is>
           <t>(?) второй адрес той же компании</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
+      <c r="K49" s="6" t="inlineStr">
         <is>
           <t>2026-09-18</t>
         </is>
@@ -2618,42 +3133,52 @@
           <t>C</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B50" s="7" t="inlineStr">
+        <is>
+          <t>спорная</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
         <is>
           <t>biysk@garant-altay.ru</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="E50" t="inlineStr">
         <is>
           <t>Гарант, информационный центр (офис Бийск)</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="F50" t="inlineStr">
         <is>
           <t>Бийск</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t>Правовые системы / бухуслуги</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="H50" t="inlineStr">
         <is>
           <t>https://2gis.ru/barnaul/firm/563478234401358</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="I50" t="inlineStr">
         <is>
           <t>garant-barnaul.ru</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="J50" t="inlineStr">
         <is>
           <t>(?) офис в Бийске</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
+      <c r="K50" t="inlineStr">
         <is>
           <t>2026-09-18</t>
         </is>
@@ -2665,143 +3190,329 @@
           <t>C</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B51" s="7" t="inlineStr">
+        <is>
+          <t>спорная</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
         <is>
           <t>gorny@garant-altay.ru</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="E51" t="inlineStr">
         <is>
           <t>Гарант, информационный центр (офис Горно-Алтайск)</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="F51" t="inlineStr">
         <is>
           <t>Горно-Алтайск</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="G51" t="inlineStr">
         <is>
           <t>Правовые системы / бухуслуги</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="H51" t="inlineStr">
         <is>
           <t>https://2gis.ru/barnaul/firm/563478234401358</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="I51" t="inlineStr">
         <is>
           <t>garant-barnaul.ru</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
+      <c r="J51" t="inlineStr">
         <is>
           <t>(?) офис в Горно-Алтайске</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
+      <c r="K51" t="inlineStr">
         <is>
           <t>2026-09-18</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="inlineStr">
+      <c r="A52" s="9" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B52" s="7" t="inlineStr">
+        <is>
+          <t>спорная</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
         <is>
           <t>info@pavelchuprakov.ru</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="E52" t="inlineStr">
         <is>
           <t>Чупраков Павел — декларации 3-НДФЛ</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>Барнаул</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Барнаул</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
         <is>
           <t>Частный специалист / декларации</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
+      <c r="H52" t="inlineStr">
         <is>
           <t>https://2gis.ru/barnaul/firm/70000001111711593</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="I52" t="inlineStr">
         <is>
           <t>pavelchuprakov.ru</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
+      <c r="J52" t="inlineStr">
         <is>
           <t>(?) личный бренд, ФИО в домене, адрес общий</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
+      <c r="K52" t="inlineStr">
         <is>
           <t>2026-09-18</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="3" t="inlineStr">
+      <c r="A53" s="9" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B53" s="7" t="inlineStr">
+        <is>
+          <t>спорная</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
         <is>
           <t>atmanoff@gmail.com</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="E53" t="inlineStr">
         <is>
           <t>Профит Флоу (Атманов)</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>Барнаул</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Барнаул</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
         <is>
           <t>Аудит / бухучёт</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="H53" t="inlineStr">
         <is>
           <t>https://2gis.ru/barnaul/firm/70000001031131458</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="I53" t="inlineStr">
         <is>
           <t>profit-flow.ru</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
+      <c r="J53" t="inlineStr">
         <is>
           <t>(?) личный адрес специалиста на сайте</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
+      <c r="K53" t="inlineStr">
         <is>
           <t>2026-09-18</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I53"/>
+  <autoFilter ref="A1:K53"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="10" t="inlineStr">
+        <is>
+          <t>Показатель</t>
+        </is>
+      </c>
+      <c r="B1" s="10" t="inlineStr">
+        <is>
+          <t>Значение</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Всего уникальных email</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Уникальных организаций</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Сегмент A — частные бухгалтеры</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Сегмент B — бухгалтерии компаний</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Сегмент C — бухгалтерские компании</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Качество: ядро</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Качество: спорная</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Вторые адреса тех же компаний</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Твёрдое ядро (ядро + осн. контакт)</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>География</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Барнаул, Бийск, Горно-Алтайск</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Источники</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2ГИС + сайты организаций</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Дата сбора</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>